--- a/data/trans_orig/IP07A12-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07A12-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos en 2007 (tasa de respuesta: 99,5%)</t>
+          <t>Menores según la frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos/as, percibida por el adulto en 2007 (tasa de respuesta: 99,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31202</t>
+          <t>30939</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48433</t>
+          <t>47214</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30225</t>
+          <t>29923</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46478</t>
+          <t>47388</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>65487</t>
+          <t>64379</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>89012</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>32,79%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36875</t>
+          <t>37050</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54858</t>
+          <t>55004</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52259</t>
+          <t>51693</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>70747</t>
+          <t>70774</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>94875</t>
+          <t>94854</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>119513</t>
+          <t>121467</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>45,25%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29293</t>
+          <t>28120</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>45581</t>
+          <t>45333</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>28256</t>
+          <t>27961</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44270</t>
+          <t>43675</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>61105</t>
+          <t>60510</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>83939</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,45%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1186</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7867</t>
+          <t>7173</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>2516</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10697</t>
+          <t>10161</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>696</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6348</t>
+          <t>6327</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2041</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9263</t>
+          <t>9607</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3827</t>
+          <t>3942</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12663</t>
+          <t>13346</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43062</t>
+          <t>42304</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62583</t>
+          <t>62139</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>56319</t>
+          <t>55184</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>76716</t>
+          <t>75819</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>104383</t>
+          <t>102569</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>132422</t>
+          <t>131961</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,2%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75197</t>
+          <t>75937</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>98165</t>
+          <t>98039</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>72576</t>
+          <t>74038</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>95105</t>
+          <t>94755</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>156113</t>
+          <t>155460</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>186861</t>
+          <t>186688</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>46,96%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34166</t>
+          <t>34437</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52590</t>
+          <t>52722</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>35398</t>
+          <t>34813</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>55302</t>
+          <t>53910</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>74625</t>
+          <t>74157</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>100666</t>
+          <t>101066</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,42%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4619</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14652</t>
+          <t>14216</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3351</t>
+          <t>3315</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12235</t>
+          <t>11300</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10091</t>
+          <t>9872</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22649</t>
+          <t>23187</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>739</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6330</t>
+          <t>6623</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7451</t>
+          <t>7389</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>2713</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10718</t>
+          <t>10911</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>78698</t>
+          <t>78941</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>105359</t>
+          <t>103820</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>89171</t>
+          <t>90751</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>116899</t>
+          <t>117555</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>174352</t>
+          <t>175950</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>212231</t>
+          <t>213962</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>32,13%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>115935</t>
+          <t>118648</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>145714</t>
+          <t>146218</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>129971</t>
+          <t>130097</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>159913</t>
+          <t>160744</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>259068</t>
+          <t>256655</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>299854</t>
+          <t>297735</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>44,71%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>67925</t>
+          <t>68341</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>92720</t>
+          <t>91515</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>67209</t>
+          <t>67006</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>91418</t>
+          <t>92220</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>140631</t>
+          <t>142519</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>175830</t>
+          <t>176008</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7410</t>
+          <t>7708</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18447</t>
+          <t>18754</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5155</t>
+          <t>4678</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14644</t>
+          <t>14016</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14250</t>
+          <t>14257</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28996</t>
+          <t>28761</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2723</t>
+          <t>2623</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10868</t>
+          <t>9901</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4455</t>
+          <t>4547</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13470</t>
+          <t>14226</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8480</t>
+          <t>8709</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20087</t>
+          <t>20910</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos en 2012 (tasa de respuesta: 98,02%)</t>
+          <t>Menores según la frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos/as, percibida por el adulto en 2012 (tasa de respuesta: 98,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>60593</t>
+          <t>60753</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>80530</t>
+          <t>81069</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>52923</t>
+          <t>52761</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>73731</t>
+          <t>73634</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>118993</t>
+          <t>118951</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>147880</t>
+          <t>147489</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>47,24%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41647</t>
+          <t>41805</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60264</t>
+          <t>60999</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42897</t>
+          <t>43047</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62690</t>
+          <t>63197</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>90480</t>
+          <t>91670</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>118609</t>
+          <t>116996</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>37,48%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20917</t>
+          <t>20702</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>37327</t>
+          <t>36687</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20194</t>
+          <t>19835</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35924</t>
+          <t>35190</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>46409</t>
+          <t>46587</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>67815</t>
+          <t>69045</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>22,12%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>1666</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9049</t>
+          <t>9045</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>4393</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13393</t>
+          <t>14367</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7808</t>
+          <t>7684</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19590</t>
+          <t>18832</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4407</t>
+          <t>4123</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11204</t>
+          <t>11699</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3341</t>
+          <t>3659</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13156</t>
+          <t>12923</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52187</t>
+          <t>52066</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>72469</t>
+          <t>72854</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>62177</t>
+          <t>61085</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>83454</t>
+          <t>82464</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>119859</t>
+          <t>121455</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>148294</t>
+          <t>149965</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,89%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52592</t>
+          <t>52792</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>73067</t>
+          <t>73335</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47288</t>
+          <t>47861</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>67937</t>
+          <t>67090</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>106153</t>
+          <t>106555</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>135527</t>
+          <t>133733</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,14%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25159</t>
+          <t>25482</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>42057</t>
+          <t>42575</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25604</t>
+          <t>25260</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>42332</t>
+          <t>42079</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>55897</t>
+          <t>55219</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>78314</t>
+          <t>78677</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,02%</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2915</t>
+          <t>2895</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11657</t>
+          <t>11793</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5009</t>
+          <t>4949</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15075</t>
+          <t>14928</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9063</t>
+          <t>9572</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21535</t>
+          <t>22760</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>606</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>6500</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7839</t>
+          <t>7718</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2567</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11613</t>
+          <t>10491</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>117966</t>
+          <t>117786</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>147421</t>
+          <t>148566</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>120179</t>
+          <t>118325</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>148416</t>
+          <t>148672</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>243996</t>
+          <t>247239</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>288369</t>
+          <t>289003</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,2%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>100243</t>
+          <t>100312</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>128659</t>
+          <t>128688</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>98118</t>
+          <t>95873</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>124521</t>
+          <t>126267</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>204397</t>
+          <t>203819</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>244001</t>
+          <t>244778</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,43%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>49612</t>
+          <t>50081</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>73517</t>
+          <t>73224</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>49631</t>
+          <t>49844</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>72883</t>
+          <t>72845</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>106404</t>
+          <t>106535</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>139201</t>
+          <t>139621</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5671</t>
+          <t>5701</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16094</t>
+          <t>16593</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11400</t>
+          <t>11553</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24443</t>
+          <t>25295</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>19497</t>
+          <t>20386</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36231</t>
+          <t>38287</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1425</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8123</t>
+          <t>8718</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5035</t>
+          <t>5242</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15158</t>
+          <t>16521</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8158</t>
+          <t>8242</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20022</t>
+          <t>19818</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos en 2016 (tasa de respuesta: 98,72%)</t>
+          <t>Menores según la frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos/as, percibida por el adulto en 2016 (tasa de respuesta: 98,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>46688</t>
+          <t>45943</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>67446</t>
+          <t>66350</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>64048</t>
+          <t>63402</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>85937</t>
+          <t>86746</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>115666</t>
+          <t>116907</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>147733</t>
+          <t>147746</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47645</t>
+          <t>47044</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67532</t>
+          <t>67831</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45575</t>
+          <t>44913</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65548</t>
+          <t>66042</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>98095</t>
+          <t>97954</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>128063</t>
+          <t>128502</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,52%</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36051</t>
+          <t>37450</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>56510</t>
+          <t>55693</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36730</t>
+          <t>37013</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>56994</t>
+          <t>57583</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>77831</t>
+          <t>78581</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>106841</t>
+          <t>106699</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,67%</t>
         </is>
       </c>
     </row>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10878</t>
+          <t>10323</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24255</t>
+          <t>24080</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5638,12 +5638,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4356</t>
+          <t>4421</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14747</t>
+          <t>14642</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17207</t>
+          <t>17214</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33991</t>
+          <t>34187</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -5736,12 +5736,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>5042</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14502</t>
+          <t>14761</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5751,12 +5751,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>687</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6246</t>
+          <t>6472</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6996</t>
+          <t>6969</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17726</t>
+          <t>18476</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39926</t>
+          <t>39757</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59388</t>
+          <t>59289</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44054</t>
+          <t>44082</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65723</t>
+          <t>65277</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>89132</t>
+          <t>88297</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>118007</t>
+          <t>117532</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,14%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45856</t>
+          <t>44959</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>66650</t>
+          <t>66557</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44568</t>
+          <t>46099</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65851</t>
+          <t>66587</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>95506</t>
+          <t>95709</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>125075</t>
+          <t>124197</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,08%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38414</t>
+          <t>38243</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>58412</t>
+          <t>58908</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>39132</t>
+          <t>39199</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>60363</t>
+          <t>59624</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>83185</t>
+          <t>84457</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>112013</t>
+          <t>112353</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,64%</t>
         </is>
       </c>
     </row>
@@ -6305,12 +6305,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8356</t>
+          <t>7900</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20350</t>
+          <t>20064</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6320,12 +6320,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8668</t>
+          <t>8627</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21471</t>
+          <t>21124</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6355,12 +6355,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19067</t>
+          <t>18622</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36194</t>
+          <t>36113</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -6418,12 +6418,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9657</t>
+          <t>9733</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>4669</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2874</t>
+          <t>2954</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11935</t>
+          <t>11887</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6503,12 +6503,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>91048</t>
+          <t>90749</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>120282</t>
+          <t>119868</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>113995</t>
+          <t>114917</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>144474</t>
+          <t>143358</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>214699</t>
+          <t>213002</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>255990</t>
+          <t>256550</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,81%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>99833</t>
+          <t>99531</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>128096</t>
+          <t>129450</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>96433</t>
+          <t>96850</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>125192</t>
+          <t>125083</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>203631</t>
+          <t>202881</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>243925</t>
+          <t>244189</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,08%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>80941</t>
+          <t>80969</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>108204</t>
+          <t>109704</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>80798</t>
+          <t>82938</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>109480</t>
+          <t>112121</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>169896</t>
+          <t>170777</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>209574</t>
+          <t>209320</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,22%</t>
         </is>
       </c>
     </row>
@@ -6987,12 +6987,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21397</t>
+          <t>21519</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38918</t>
+          <t>39387</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14837</t>
+          <t>14473</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30543</t>
+          <t>29855</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7037,12 +7037,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>40249</t>
+          <t>40644</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>63935</t>
+          <t>65543</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -7100,12 +7100,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8659</t>
+          <t>7990</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20338</t>
+          <t>20383</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1424</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8825</t>
+          <t>8067</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7150,12 +7150,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11974</t>
+          <t>12069</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>25886</t>
+          <t>26060</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07A12-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07A12-Edad-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos/as, percibida por el adulto en 2007 (tasa de respuesta: 99,5%)</t>
+          <t>Menores según la frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos/as, percibida por el/la adulto/a [KIDSCREEN 20] en 2007 (tasa de respuesta: 99,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>37911</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>29488</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>46104</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>26,79%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>20,84%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>32,58%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>38376</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>30939</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>47214</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>29761</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>46801</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>30,24%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>24,38%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>37,21%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>37911</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>29923</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>47388</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>26,79%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>64379</t>
+          <t>65232</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>88116</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,83%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>61600</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>52881</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>71599</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>43,53%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>37,37%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>50,59%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>45767</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>37050</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>55004</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>36907</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>54965</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>36,07%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>29,2%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>43,35%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>61600</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>51693</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>70774</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>43,53%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>94854</t>
+          <t>93544</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>121467</t>
+          <t>119638</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>44,57%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>35349</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>27789</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>43717</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>24,98%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>19,64%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>30,89%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>36719</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>28120</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>45333</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>28427</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>44507</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>28,94%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>22,16%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>35,73%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>35349</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>27961</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>43675</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>24,98%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>60510</t>
+          <t>60957</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>84421</t>
+          <t>83212</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,0%</t>
         </is>
       </c>
     </row>
@@ -1061,72 +1061,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1935</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5174</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,66%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>3313</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1186</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7173</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1213</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7368</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,61%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,65%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1935</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5080</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2516</t>
+          <t>2304</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10161</t>
+          <t>9619</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -1174,72 +1174,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4719</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2041</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>10339</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3,33%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>7,31%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>2719</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>696</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6327</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>6679</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>2,14%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4,99%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>4719</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>9607</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>3,33%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3942</t>
+          <t>4016</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13346</t>
+          <t>12599</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>126894</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>126894</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>126894</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>65662</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>55814</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>78562</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>32,18%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>27,35%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>38,5%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>52245</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>42304</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>62139</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>43496</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>62420</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>27,01%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>21,87%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>32,12%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>65662</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>55184</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>75819</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>32,18%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>102569</t>
+          <t>103531</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>131961</t>
+          <t>133530</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,59%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>84063</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>71475</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>94351</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>41,19%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>35,02%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>46,23%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>86964</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>75937</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>98039</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>75421</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>97292</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>44,95%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>39,25%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>50,68%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>84063</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>94755</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>41,19%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>155460</t>
+          <t>155567</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>186688</t>
+          <t>186696</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>44279</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>35704</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>54576</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>21,7%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>17,5%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>26,74%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>42893</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>34437</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>52722</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>33662</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>52234</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>22,17%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>17,8%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>27,25%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>44279</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>34813</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>53910</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>21,7%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>74157</t>
+          <t>73204</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>101066</t>
+          <t>99171</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>24,95%</t>
         </is>
       </c>
     </row>
@@ -1743,72 +1743,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6731</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3425</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12081</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5,92%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>8666</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5033</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>14216</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>4788</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>14438</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>4,48%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,35%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>6731</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>3315</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>11300</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,3%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9872</t>
+          <t>10258</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23187</t>
+          <t>22142</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -1856,72 +1856,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3337</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1309</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6855</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>2688</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>739</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6623</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>733</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>7326</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>1,39%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>3337</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>1309</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>7389</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>2740</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10911</t>
+          <t>11367</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>204072</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>204072</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>204072</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>285</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>193455</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>193455</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>193455</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>204072</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>204072</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>204072</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>103572</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>118285</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>29,97%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>26,01%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>34,23%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>90621</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>78941</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>103820</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>78341</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>104510</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>28,29%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>24,64%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>32,41%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>103572</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>90751</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>117555</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>29,97%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>175950</t>
+          <t>176959</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>213962</t>
+          <t>215226</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,32%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>145663</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>132480</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>162528</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>42,15%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>38,33%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>47,03%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>195</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>132730</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>118648</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>146218</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>119045</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>147304</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>41,43%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>37,04%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>45,64%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>145663</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>130097</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>160744</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>42,15%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>256655</t>
+          <t>259069</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>297735</t>
+          <t>298459</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,82%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>79629</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>67366</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>92819</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>23,04%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>19,49%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>26,86%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>79611</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>68341</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>91515</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>66626</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>92088</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>24,85%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>21,33%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>28,57%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>79629</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>67006</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>92220</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>23,04%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>142519</t>
+          <t>141358</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>176008</t>
+          <t>177480</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,65%</t>
         </is>
       </c>
     </row>
@@ -2425,72 +2425,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>8666</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>4782</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>14285</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>4,13%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>11979</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>7708</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>18754</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>7349</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>18342</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>3,74%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>5,85%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>8666</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>4678</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>14016</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>2,51%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14257</t>
+          <t>14539</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28761</t>
+          <t>29709</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -2538,107 +2538,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>8057</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>4164</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>13599</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>3,94%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>5407</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>2623</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>9901</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>2581</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>10219</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>1,69%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>13464</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>8731</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>20559</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
         <is>
           <t>3,09%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>8057</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>4547</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>14226</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>4,12%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>13464</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>8709</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>20910</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>2,02%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>345587</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>345587</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>345587</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>475</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>320349</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>320349</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>320349</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>345587</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>345587</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>345587</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2813,13 +2813,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos/as, percibida por el adulto en 2012 (tasa de respuesta: 98,02%)</t>
+          <t>Menores según la frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos/as, percibida por el/la adulto/a [KIDSCREEN 20] en 2012 (tasa de respuesta: 98,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2830,7 +2830,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2998,72 +2998,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>62819</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>53081</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>73264</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>40,1%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>33,88%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>46,76%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>70592</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>60753</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>81069</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>59821</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>80264</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>45,39%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>39,07%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>52,13%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>62819</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>52761</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>73634</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>40,1%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>118951</t>
+          <t>118609</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>147489</t>
+          <t>148373</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,53%</t>
         </is>
       </c>
     </row>
@@ -3111,72 +3111,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>52431</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>43494</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>62585</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>33,47%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>27,76%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>39,95%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>50814</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>41805</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>60999</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>41257</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>60620</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>32,67%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>26,88%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>39,22%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>52431</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>43047</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>63197</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>33,47%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>91670</t>
+          <t>90423</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116996</t>
+          <t>117672</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,69%</t>
         </is>
       </c>
     </row>
@@ -3224,72 +3224,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>27335</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>20204</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>35399</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>17,45%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>12,9%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>22,59%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>28561</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>20702</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>36687</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>20877</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>37310</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>18,37%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>13,31%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>23,59%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>27335</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>19835</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>35190</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>17,45%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>46587</t>
+          <t>45612</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>69045</t>
+          <t>67704</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>21,69%</t>
         </is>
       </c>
     </row>
@@ -3337,72 +3337,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8071</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3941</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>14179</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,15%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,52%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,05%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>4299</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1666</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9045</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1507</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>9202</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,76%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,82%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>8071</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>4393</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>14367</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>5,15%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7684</t>
+          <t>7724</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18832</t>
+          <t>19672</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -3450,72 +3450,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6017</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2762</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>11980</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3,84%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>7,65%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>1249</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4123</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4069</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,8%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>6017</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>2640</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>11699</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>3,84%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12923</t>
+          <t>13069</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -3563,57 +3563,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>156674</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>156674</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>156674</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>155514</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>155514</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>155514</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>156674</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>156674</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>156674</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3680,72 +3680,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>71791</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>61300</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>82443</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>40,98%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>34,99%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>47,06%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>62277</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>52066</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>72854</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>52795</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>74063</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>37,4%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>31,26%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>43,75%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>71791</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>61085</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>82464</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>40,98%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>121455</t>
+          <t>119858</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>149965</t>
+          <t>148471</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>43,45%</t>
         </is>
       </c>
     </row>
@@ -3793,72 +3793,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>57682</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>48075</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>67414</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>32,93%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>27,44%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>38,48%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>62985</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>52792</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>73335</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>53152</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>73013</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>37,82%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>31,7%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>44,04%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>57682</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>47861</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>67090</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>32,93%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>106555</t>
+          <t>106804</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>133733</t>
+          <t>135103</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>39,54%</t>
         </is>
       </c>
     </row>
@@ -3906,72 +3906,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>33346</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>25704</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>42681</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>19,03%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>14,67%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>24,36%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>32981</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>25482</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>42575</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>25244</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>42136</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>19,8%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>15,3%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>25,57%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>33346</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>25260</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>42079</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>19,03%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>55219</t>
+          <t>54953</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>78677</t>
+          <t>80667</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,61%</t>
         </is>
       </c>
     </row>
@@ -4019,107 +4019,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8970</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4695</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>15238</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5,12%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,7%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>5942</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2895</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>11793</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2425</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>11485</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,57%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,08%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>8970</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>4949</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>14928</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,12%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>6,9%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>14912</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>9643</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>22248</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>4,36%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>2,82%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>8,52%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>14912</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>9572</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>22760</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -4132,72 +4132,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3397</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1175</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>7622</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>4,35%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>2350</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>606</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6500</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>6874</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>1,41%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,36%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3,9%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>3397</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>1164</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>7718</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2782</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10491</t>
+          <t>11567</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -4245,57 +4245,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>175187</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>175187</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>175187</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>166535</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>166535</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>166535</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>175187</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>175187</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>175187</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4362,72 +4362,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>134610</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>119533</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>148466</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>40,56%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>36,02%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>44,74%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>132870</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>117786</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>148566</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>119155</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>147566</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>41,26%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>36,57%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>46,13%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>134610</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>118325</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>148672</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>40,56%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>247239</t>
+          <t>248251</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>289003</t>
+          <t>288048</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>44,05%</t>
         </is>
       </c>
     </row>
@@ -4475,72 +4475,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>110113</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>96641</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>124733</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>33,18%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>29,12%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>37,59%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>113799</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>100312</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>128688</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>100134</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>128165</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>35,34%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>31,15%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>39,96%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>110113</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>95873</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>126267</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>33,18%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>203819</t>
+          <t>204128</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>244778</t>
+          <t>244356</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,37%</t>
         </is>
       </c>
     </row>
@@ -4588,72 +4588,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>60682</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>49895</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>73915</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>18,29%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>15,03%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>22,27%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>61541</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>50081</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>73224</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>48871</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>72672</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>19,11%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>15,55%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>22,74%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>60682</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>49844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>72845</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>18,29%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>106535</t>
+          <t>106492</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>139621</t>
+          <t>138659</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,2%</t>
         </is>
       </c>
     </row>
@@ -4701,72 +4701,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>17042</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>11311</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>24632</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>5,14%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>7,42%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>10241</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>5701</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>16593</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>5872</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>16646</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>3,18%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>5,15%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>17042</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>11553</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>25295</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>5,14%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20386</t>
+          <t>18676</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38287</t>
+          <t>35668</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -4814,72 +4814,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>9414</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>5133</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>15900</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2,84%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>4,79%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>3599</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1425</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>8718</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>1359</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>8343</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>1,12%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2,71%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>9414</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>5242</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>16521</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8242</t>
+          <t>7541</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19818</t>
+          <t>20011</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -4927,57 +4927,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>483</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>331861</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>331861</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>331861</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>457</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>322050</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>322050</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>322050</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>483</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>331861</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>331861</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>331861</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5089,13 +5089,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos/as, percibida por el adulto en 2016 (tasa de respuesta: 98,72%)</t>
+          <t>Menores según la frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos/as, percibida por el/la adulto/a [KIDSCREEN 20] en 2016 (tasa de respuesta: 98,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5106,7 +5106,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5274,72 +5274,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>74810</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>64784</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>87116</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>39,94%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>34,59%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>46,51%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>56292</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>45943</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>66350</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>45555</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>66995</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>30,45%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>24,85%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>35,89%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>74810</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>63402</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>86746</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>39,94%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>116907</t>
+          <t>117072</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>147746</t>
+          <t>146999</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>39,49%</t>
         </is>
       </c>
     </row>
@@ -5387,72 +5387,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>55097</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>45989</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>66157</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>29,41%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>24,55%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>35,32%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>57487</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>47044</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>67831</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>47523</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>68444</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>31,09%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>25,44%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>36,69%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>55097</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>44913</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>66042</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>29,41%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>97954</t>
+          <t>97909</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>128502</t>
+          <t>127621</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,29%</t>
         </is>
       </c>
     </row>
@@ -5500,72 +5500,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>46358</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>36106</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>55920</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>24,75%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>19,28%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>29,85%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>46029</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>37450</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>55693</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>36424</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>56658</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>24,89%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>20,25%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>30,12%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>46358</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>37013</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>57583</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>24,75%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>78581</t>
+          <t>77741</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>106699</t>
+          <t>106387</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,58%</t>
         </is>
       </c>
     </row>
@@ -5613,72 +5613,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8412</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4323</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>13869</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,49%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,4%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>16340</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>10323</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>24080</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>11042</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>24133</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>8,84%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,58%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>13,02%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>8412</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>4421</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>14642</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,49%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17214</t>
+          <t>17451</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34187</t>
+          <t>34204</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -5726,72 +5726,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2636</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6326</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3,38%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>8747</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>5042</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>14761</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>4607</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>14692</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>4,73%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7,98%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>2636</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>6472</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6969</t>
+          <t>6833</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18476</t>
+          <t>17583</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -5839,57 +5839,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>187313</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>187313</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>187313</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>265</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>184895</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>184895</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>184895</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>187313</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>187313</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>187313</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5956,72 +5956,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>53874</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>44016</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>64064</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>31,06%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>25,38%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>36,93%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>49197</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>39757</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>59289</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>40332</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>58842</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>28,81%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>23,28%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>34,71%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>53874</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>44082</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>65277</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>31,06%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>88297</t>
+          <t>90545</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>117532</t>
+          <t>117871</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,24%</t>
         </is>
       </c>
     </row>
@@ -6069,72 +6069,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>55138</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>45492</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>65601</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>31,79%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>26,23%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>37,82%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>55554</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>44959</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>66557</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>46217</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>65904</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>32,53%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>26,32%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>38,97%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>55138</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>46099</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>66587</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>31,79%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>95709</t>
+          <t>96871</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>124197</t>
+          <t>126017</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,61%</t>
         </is>
       </c>
     </row>
@@ -6182,72 +6182,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>49281</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>40166</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>59344</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>28,41%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>23,16%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>34,21%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>48002</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>38243</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>58908</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>38690</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>58619</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>28,11%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>22,39%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>34,49%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>49281</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>39199</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>59624</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>28,41%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>84457</t>
+          <t>84064</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>112353</t>
+          <t>112698</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,74%</t>
         </is>
       </c>
     </row>
@@ -6300,67 +6300,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>13770</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8643</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>20650</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7,94%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,98%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11,9%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>13099</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>7900</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>20064</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>8460</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>20521</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>7,67%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,63%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>11,75%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>13770</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>8627</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>21124</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>7,94%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18622</t>
+          <t>19225</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36113</t>
+          <t>36409</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -6408,72 +6408,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1396</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4483</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>4936</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2327</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>9733</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2115</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>9594</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>2,89%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>5,7%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1396</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4669</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2954</t>
+          <t>3059</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11887</t>
+          <t>11284</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6503,12 +6503,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -6521,57 +6521,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>173460</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>173460</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>173460</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>170789</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>170789</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>170789</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>173460</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>173460</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>173460</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6638,72 +6638,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>128684</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>114692</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>143906</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>35,67%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>31,79%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>39,89%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>105489</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>90749</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>119868</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>91022</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>121404</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>29,66%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>25,51%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>33,7%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>128684</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>114917</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>143358</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>35,67%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>213002</t>
+          <t>211519</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>256550</t>
+          <t>253835</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,43%</t>
         </is>
       </c>
     </row>
@@ -6751,72 +6751,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>110235</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>94096</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>124330</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>30,56%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>26,08%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>34,46%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>161</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>113041</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>99531</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>129450</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>98327</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>129366</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>31,78%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>27,98%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>36,39%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>110235</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>96850</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>125083</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>30,56%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>202881</t>
+          <t>202057</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>244189</t>
+          <t>243243</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>33,95%</t>
         </is>
       </c>
     </row>
@@ -6864,72 +6864,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>95639</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>82124</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>109931</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>26,51%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>22,76%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>30,47%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>94031</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>80969</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>109704</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>81202</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>108749</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>26,44%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>22,76%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>30,84%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>95639</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>82938</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>112121</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>26,51%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>170777</t>
+          <t>170260</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>209320</t>
+          <t>211255</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,49%</t>
         </is>
       </c>
     </row>
@@ -6977,72 +6977,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>22182</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>15224</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>30602</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>6,15%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>4,22%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>8,48%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>29440</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>21519</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>39387</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>21271</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>39325</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>8,28%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>6,05%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>11,07%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>22182</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>14473</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>29855</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>40644</t>
+          <t>40945</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>65543</t>
+          <t>63926</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,92%</t>
         </is>
       </c>
     </row>
@@ -7090,72 +7090,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>4032</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1614</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>8101</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>13683</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>7990</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>20383</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>8612</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>20454</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>3,85%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>5,73%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>4032</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>1424</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>8067</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12069</t>
+          <t>11687</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>26060</t>
+          <t>25273</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -7203,57 +7203,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>360773</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>360773</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>360773</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>508</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>355684</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>355684</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>355684</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>495</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>360773</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>360773</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>360773</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
